--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>115632575</v>
       </c>
       <c r="B3" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,240 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126205967</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>467671</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544363</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretå påtall bredvid blötan.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126205780</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57652</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Edsbackemossen, Edsbackemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>467751</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6544325</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på tall I kanten av låg ås</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>126205967</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>126205780</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>126205967</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>126205780</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115632414</v>
+        <v>114947148</v>
       </c>
       <c r="B2" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogskärr (Skogskärr), Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467565</v>
+        <v>467673</v>
       </c>
       <c r="R2" t="n">
-        <v>6544376</v>
+        <v>6544370</v>
       </c>
       <c r="S2" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +748,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hackringar av tretåig hackspett på 4 st granar. Även färsk barkfläkning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115632575</v>
+        <v>115632414</v>
       </c>
       <c r="B3" t="n">
-        <v>56563</v>
+        <v>104737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +811,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogskärr, Skogskärr, Nrk</t>
+          <t>Skogskärr (Skogskärr), Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467674</v>
+        <v>467565</v>
       </c>
       <c r="R3" t="n">
-        <v>6544294</v>
+        <v>6544376</v>
       </c>
       <c r="S3" t="n">
         <v>40</v>
@@ -862,27 +865,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2024-03-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Mycket och färsk spillning precis vid kolbotten.</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +907,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126205967</v>
+        <v>115632575</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>56563</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Skogskärr, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467671</v>
+        <v>467674</v>
       </c>
       <c r="R4" t="n">
-        <v>6544363</v>
+        <v>6544294</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +982,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretå påtall bredvid blötan.</t>
+          <t>Mycket och färsk spillning precis vid kolbotten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,7 +1029,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126205780</v>
+        <v>126205967</v>
       </c>
       <c r="B5" t="n">
         <v>57657</v>
@@ -1062,14 +1065,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Edsbackemossen, Edsbackemossen, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467751</v>
+        <v>467671</v>
       </c>
       <c r="R5" t="n">
-        <v>6544325</v>
+        <v>6544363</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1101,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1114,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett på tall I kanten av låg ås</t>
+          <t>Färska ringhack av tretå påtall bredvid blötan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1134,1651 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126205780</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Edsbackemossen, Edsbackemossen, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>467751</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6544325</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på tall I kanten av låg ås</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>David Tverling</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130097720</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>467470</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6544250</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre födohack på klen granlåga</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130098648</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>467595</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6544219</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre födohack på stående död gran</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130106307</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>467681</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6544319</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130106554</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Anderstorp, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>467682</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6544371</v>
+      </c>
+      <c r="S10" t="n">
+        <v>19</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hackringar av tretåig hackspett på 4 st granar i kanten inom avverkn anm. Även färsk barkfläkning., se bilder i annat fynd.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130097419</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Skogskärr S, Skogskärr S, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>467444</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6544262</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen på stående död tall</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130097202</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>467478</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6544329</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska födohack på rötad stubbe.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130097242</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>467478</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6544341</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska födohack på rötad stubbe</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130099210</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>467557</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6544424</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska födohack på låga av tall</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130098966</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Anderstorpsvägen N, Anderstorpsvägen N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>467624</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6544325</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130106657</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Anderstorp, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>467683</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6544369</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130098769</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>467589</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6544293</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130096972</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>467483</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6544396</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen av död tall.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130106569</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Anderstorp, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>467677</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6544370</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-02-21</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -2314,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130106657</v>
+        <v>130098769</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2350,14 +2350,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Anderstorp, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467683</v>
+        <v>467589</v>
       </c>
       <c r="R16" t="n">
-        <v>6544369</v>
+        <v>6544293</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130098769</v>
+        <v>130106657</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,16 +2442,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2467,14 +2467,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467589</v>
+        <v>467683</v>
       </c>
       <c r="R17" t="n">
-        <v>6544293</v>
+        <v>6544369</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2501,27 +2501,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -1846,7 +1846,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130099210</v>
+        <v>130097202</v>
       </c>
       <c r="B12" t="n">
         <v>57738</v>
@@ -1882,14 +1882,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467557</v>
+        <v>467478</v>
       </c>
       <c r="R12" t="n">
-        <v>6544424</v>
+        <v>6544329</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall</t>
+          <t>Färska födohack på rötad stubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,7 +1963,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130097202</v>
+        <v>130099210</v>
       </c>
       <c r="B13" t="n">
         <v>57738</v>
@@ -1999,14 +1999,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogskärr S, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467478</v>
+        <v>467557</v>
       </c>
       <c r="R13" t="n">
-        <v>6544329</v>
+        <v>6544424</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska födohack på rötad stubbe.</t>
+          <t>Färska födohack på låga av tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2314,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130098769</v>
+        <v>130106657</v>
       </c>
       <c r="B16" t="n">
-        <v>57738</v>
+        <v>57741</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2350,14 +2350,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467589</v>
+        <v>467683</v>
       </c>
       <c r="R16" t="n">
-        <v>6544293</v>
+        <v>6544369</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130106657</v>
+        <v>130098769</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57738</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,16 +2442,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2467,14 +2467,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Anderstorp, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467683</v>
+        <v>467589</v>
       </c>
       <c r="R17" t="n">
-        <v>6544369</v>
+        <v>6544293</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2501,27 +2501,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114947148</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>130097720</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1383,7 +1383,7 @@
         <v>130098648</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>130106307</v>
       </c>
       <c r="B9" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>130106554</v>
       </c>
       <c r="B10" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>130097419</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>130097202</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130099210</v>
+        <v>130097242</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,14 +1999,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467557</v>
+        <v>467478</v>
       </c>
       <c r="R13" t="n">
-        <v>6544424</v>
+        <v>6544341</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall</t>
+          <t>Färska födohack på rötad stubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,10 +2080,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130097242</v>
+        <v>130099210</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2116,14 +2116,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skogskärr S, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467478</v>
+        <v>467557</v>
       </c>
       <c r="R14" t="n">
-        <v>6544341</v>
+        <v>6544424</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska födohack på rötad stubbe</t>
+          <t>Färska födohack på låga av tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2200,7 +2200,7 @@
         <v>130098966</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>130106657</v>
       </c>
       <c r="B16" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2434,7 +2434,7 @@
         <v>130098769</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>130096972</v>
       </c>
       <c r="B18" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>130106569</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -2314,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130098769</v>
+        <v>130106657</v>
       </c>
       <c r="B16" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,16 +2325,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2350,14 +2350,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467589</v>
+        <v>467683</v>
       </c>
       <c r="R16" t="n">
-        <v>6544293</v>
+        <v>6544369</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2384,27 +2384,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130106657</v>
+        <v>130098769</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,16 +2442,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2467,14 +2467,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Anderstorp, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467683</v>
+        <v>467589</v>
       </c>
       <c r="R17" t="n">
-        <v>6544369</v>
+        <v>6544293</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2501,27 +2501,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -1846,7 +1846,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130097242</v>
+        <v>130097202</v>
       </c>
       <c r="B12" t="n">
         <v>57823</v>
@@ -1889,7 +1889,7 @@
         <v>467478</v>
       </c>
       <c r="R12" t="n">
-        <v>6544341</v>
+        <v>6544329</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på rötad stubbe</t>
+          <t>Färska födohack på rötad stubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,7 +1963,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130097202</v>
+        <v>130097242</v>
       </c>
       <c r="B13" t="n">
         <v>57823</v>
@@ -2006,7 +2006,7 @@
         <v>467478</v>
       </c>
       <c r="R13" t="n">
-        <v>6544329</v>
+        <v>6544341</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,12 +2048,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska födohack på rötad stubbe.</t>
+          <t>Färska födohack på rötad stubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3009,6 +3009,347 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131508480</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Anderstorp, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>467593</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6544257</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre födohack vid basen stående tall.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131508252</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5197</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Anderstorp, Anderstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>467624</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6544267</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnag.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131508977</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Anderstorp, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>467600</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6544217</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -3014,7 +3014,7 @@
         <v>131508480</v>
       </c>
       <c r="B22" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>131508977</v>
       </c>
       <c r="B24" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -3014,7 +3014,7 @@
         <v>131508480</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>131508977</v>
       </c>
       <c r="B24" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114947148</v>
+        <v>130096972</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -704,27 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Anderstorp, Skogskärr, Nrk</t>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467673</v>
+        <v>467483</v>
       </c>
       <c r="R2" t="n">
-        <v>6544370</v>
+        <v>6544396</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +745,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hackringar av tretåig hackspett på 4 st granar. Även färsk barkfläkning.</t>
+          <t>Färska födohack vid basen av död tall.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115632414</v>
+        <v>130097202</v>
       </c>
       <c r="B3" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,37 +803,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogskärr (Skogskärr), Nrk</t>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467565</v>
+        <v>467478</v>
       </c>
       <c r="R3" t="n">
-        <v>6544376</v>
+        <v>6544329</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +862,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-17</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska födohack på rötad stubbe.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115632575</v>
+        <v>130097242</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,42 +920,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogskärr, Skogskärr, Nrk</t>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467674</v>
+        <v>467478</v>
       </c>
       <c r="R4" t="n">
-        <v>6544294</v>
+        <v>6544341</v>
       </c>
       <c r="S4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,27 +979,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mycket och färsk spillning precis vid kolbotten.</t>
+          <t>Färska födohack på rötad stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,27 +1026,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126205967</v>
+        <v>130097419</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1065,14 +1062,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Skogskärr S, Skogskärr S, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467671</v>
+        <v>467444</v>
       </c>
       <c r="R5" t="n">
-        <v>6544363</v>
+        <v>6544262</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1099,27 +1096,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretå påtall bredvid blötan.</t>
+          <t>Färska födohack vid basen på stående död tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,27 +1143,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126205780</v>
+        <v>130097720</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1177,19 +1174,19 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Edsbackemossen, Edsbackemossen, Nrk</t>
+          <t>Skogskärr S, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>467751</v>
+        <v>467470</v>
       </c>
       <c r="R6" t="n">
-        <v>6544325</v>
+        <v>6544250</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1216,27 +1213,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett på tall I kanten av låg ås</t>
+          <t>Äldre födohack på klen granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,26 +1248,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Therese Steiner</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130097720</v>
+        <v>130098648</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1303,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467470</v>
+        <v>467595</v>
       </c>
       <c r="R7" t="n">
-        <v>6544250</v>
+        <v>6544219</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1338,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,12 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre födohack på klen granlåga</t>
+          <t>Äldre födohack på stående död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,14 +1377,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130098648</v>
+        <v>130098769</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1411,19 +1408,19 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skogskärr S, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>467595</v>
+        <v>467589</v>
       </c>
       <c r="R8" t="n">
-        <v>6544219</v>
+        <v>6544293</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1455,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1462,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre födohack på stående död gran</t>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130106307</v>
+        <v>130098966</v>
       </c>
       <c r="B9" t="n">
-        <v>57016</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,39 +1505,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Anderstorpsvägen N, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>467681</v>
+        <v>467624</v>
       </c>
       <c r="R9" t="n">
-        <v>6544319</v>
+        <v>6544325</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1567,22 +1564,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,27 +1611,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130106554</v>
+        <v>130099210</v>
       </c>
       <c r="B10" t="n">
-        <v>57826</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1638,27 +1640,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Anderstorp, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467682</v>
+        <v>467557</v>
       </c>
       <c r="R10" t="n">
-        <v>6544371</v>
+        <v>6544424</v>
       </c>
       <c r="S10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,27 +1681,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hackringar av tretåig hackspett på 4 st granar i kanten inom avverkn anm. Även färsk barkfläkning., se bilder i annat fynd.</t>
+          <t>Färska födohack på låga av tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,14 +1728,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130097419</v>
+        <v>131200433</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1765,14 +1764,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skogskärr S, Skogskärr S, Nrk</t>
+          <t>Anderstorp, Anderstorp, Nrk</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467444</v>
+        <v>467501</v>
       </c>
       <c r="R11" t="n">
-        <v>6544262</v>
+        <v>6544246</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1799,27 +1798,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen på stående död tall</t>
+          <t>Färska födohack vid basen på döende tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,14 +1845,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130097202</v>
+        <v>131508480</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1877,19 +1876,19 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skogskärr S, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467478</v>
+        <v>467593</v>
       </c>
       <c r="R12" t="n">
-        <v>6544329</v>
+        <v>6544257</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1916,27 +1915,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på rötad stubbe.</t>
+          <t>Äldre födohack vid basen stående tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,14 +1962,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130097242</v>
+        <v>131508977</v>
       </c>
       <c r="B13" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1994,19 +1993,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skogskärr S, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467478</v>
+        <v>467600</v>
       </c>
       <c r="R13" t="n">
-        <v>6544341</v>
+        <v>6544217</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2033,27 +2032,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färska födohack på rötad stubbe</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,10 +2074,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130099210</v>
+        <v>114947148</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2091,16 +2085,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2109,24 +2103,27 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467557</v>
+        <v>467673</v>
       </c>
       <c r="R14" t="n">
-        <v>6544424</v>
+        <v>6544370</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2150,27 +2147,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska födohack på låga av tall</t>
+          <t>Hackringar av tretåig hackspett på 4 st granar. Även färsk barkfläkning.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130098966</v>
+        <v>126205780</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2208,16 +2205,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2233,11 +2230,11 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Anderstorpsvägen N, Nrk</t>
+          <t>Edsbackemossen, Edsbackemossen, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467624</v>
+        <v>467751</v>
       </c>
       <c r="R15" t="n">
         <v>6544325</v>
@@ -2267,27 +2264,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Färska ringhack av tretåig hackspett på tall I kanten av låg ås</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,22 +2299,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Therese Steiner</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130106657</v>
+        <v>126205967</v>
       </c>
       <c r="B16" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2350,14 +2347,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Anderstorp, Skogskärr, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467683</v>
+        <v>467671</v>
       </c>
       <c r="R16" t="n">
-        <v>6544369</v>
+        <v>6544363</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2384,27 +2381,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-02-21</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
+          <t>Färska ringhack av tretå påtall bredvid blötan.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,10 +2428,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130098769</v>
+        <v>130106554</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,16 +2439,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2460,24 +2457,27 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467589</v>
+        <v>467682</v>
       </c>
       <c r="R17" t="n">
-        <v>6544293</v>
+        <v>6544371</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2501,27 +2501,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Hackringar av tretåig hackspett på 4 st granar i kanten inom avverkn anm. Även färsk barkfläkning., se bilder i annat fynd.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130096972</v>
+        <v>130106569</v>
       </c>
       <c r="B18" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2559,16 +2559,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2584,14 +2584,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skogskärr S, Skogskärr, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467483</v>
+        <v>467677</v>
       </c>
       <c r="R18" t="n">
-        <v>6544396</v>
+        <v>6544370</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2618,27 +2618,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen av död tall.</t>
+          <t>Färska hackringar med savflöde av tretåig hackspett på 4 st granar. Även färsk barkfläkning. se bilder i annat fynd bredvid.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2665,10 +2665,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130106569</v>
+        <v>130106657</v>
       </c>
       <c r="B19" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467677</v>
+        <v>467683</v>
       </c>
       <c r="R19" t="n">
-        <v>6544370</v>
+        <v>6544369</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2782,27 +2782,27 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131199758</v>
+        <v>131200531</v>
       </c>
       <c r="B20" t="n">
-        <v>5197</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2813,19 +2813,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Anderstorp, Anderstorp, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467630</v>
+        <v>467496</v>
       </c>
       <c r="R20" t="n">
-        <v>6544255</v>
+        <v>6544275</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Äldre gnagspår och kläckhål på stående död gran</t>
+          <t>Äldre ringhack på tall. Längre upp färska ringhack med torkat savflöde. Tallen står precis på gränsen till blötan. Bredvid klen hög gran som skymmer. Syns bäst fr öster.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2899,45 +2899,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131199884</v>
+        <v>131200654</v>
       </c>
       <c r="B21" t="n">
-        <v>4773</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Anderstorp, Anderstorp, Nrk</t>
+          <t>Anderstorp, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>467729</v>
+        <v>467509</v>
       </c>
       <c r="R21" t="n">
-        <v>6544345</v>
+        <v>6544343</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2969,7 +2974,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2979,12 +2984,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Gnagspår och kläckhål i stående död gran</t>
+          <t>Färska ringhack av tretåig hackspett på klenare tall i blötan. Rikligt med torkad rinnande kåda.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3011,53 +3016,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131508480</v>
+        <v>115632575</v>
       </c>
       <c r="B22" t="n">
-        <v>57911</v>
+        <v>57141</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Anderstorp, Skogskärr, Nrk</t>
+          <t>Skogskärr, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467593</v>
+        <v>467674</v>
       </c>
       <c r="R22" t="n">
-        <v>6544257</v>
+        <v>6544294</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3081,27 +3086,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Äldre födohack vid basen stående tall.</t>
+          <t>Mycket och färsk spillning precis vid kolbotten.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3128,10 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131508252</v>
+        <v>130106307</v>
       </c>
       <c r="B23" t="n">
-        <v>5199</v>
+        <v>57141</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3139,34 +3144,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105930</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Anderstorp, Anderstorp, Nrk</t>
+          <t>Anderstorpsvägen N, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467624</v>
+        <v>467681</v>
       </c>
       <c r="R23" t="n">
-        <v>6544267</v>
+        <v>6544319</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3193,27 +3203,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:46</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Kläckhål och gnag.</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3240,38 +3245,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131508977</v>
+        <v>131508997</v>
       </c>
       <c r="B24" t="n">
-        <v>57911</v>
+        <v>57141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3280,7 +3285,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>467600</v>
+        <v>467649</v>
       </c>
       <c r="R24" t="n">
         <v>6544217</v>
@@ -3315,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3325,7 +3330,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sten.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3349,6 +3359,454 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131199884</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Anderstorp, Anderstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>467729</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6544345</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gnagspår och kläckhål i stående död gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131199758</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Anderstorp, Anderstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>467630</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6544255</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår och kläckhål på stående död gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131508252</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Anderstorp, Anderstorp, Nrk</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>467624</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6544267</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kläckhål och gnag.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115632414</v>
+      </c>
+      <c r="B28" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Skogskärr, Skogskärr, Nrk</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>467565</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6544376</v>
+      </c>
+      <c r="S28" t="n">
+        <v>40</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-17</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38916-2023 artfynd.xlsx
+++ b/artfynd/A 38916-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130096972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130097202</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130097242</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130097419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130097720</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130098648</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1491,6 +1526,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130098769</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1608,6 +1648,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130098966</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130099210</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1842,6 +1892,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131200433</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1959,6 +2014,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131508480</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2071,6 +2131,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131508977</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2191,6 +2256,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114947148</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2308,6 +2378,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126205780</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2425,6 +2500,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126205967</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2545,6 +2625,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106554</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2662,6 +2747,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106569</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2779,6 +2869,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106657</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2896,6 +2991,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131200531</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3013,6 +3113,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131200654</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3130,6 +3235,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632575</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3242,6 +3352,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106307</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3359,6 +3474,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131508997</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3471,6 +3591,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131199884</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3588,6 +3713,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131199758</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3700,6 +3830,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131508252</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3807,8 +3942,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115632414</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>